--- a/resolveIssues/ig/StructureDefinition-fr-observation-survey-document.xlsx
+++ b/resolveIssues/ig/StructureDefinition-fr-observation-survey-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:56:38+00:00</t>
+    <t>2026-06-04T08:54:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -692,6 +692,15 @@
     <t>Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/observation-category"/&gt;
+    &lt;code value="survey"/&gt;
+    &lt;display value="Survey"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
@@ -742,13 +751,6 @@
   </si>
   <si>
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://terminology.hl7.org/CodeSystem/observation-category"/&gt;
-  &lt;code value="survey"/&gt;
-  &lt;display value="Survey"/&gt;
-&lt;/valueCoding&gt;</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -4795,7 +4797,7 @@
         <v>82</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>82</v>
@@ -4813,10 +4815,10 @@
         <v>117</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>82</v>
@@ -4858,10 +4860,10 @@
         <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
@@ -4869,10 +4871,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4898,10 +4900,10 @@
         <v>191</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4976,7 +4978,7 @@
         <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4987,10 +4989,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5019,7 +5021,7 @@
         <v>140</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>142</v>
@@ -5063,7 +5065,7 @@
         <v>198</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>82</v>
@@ -5096,7 +5098,7 @@
         <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -5107,10 +5109,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5133,19 +5135,19 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -5155,7 +5157,7 @@
         <v>82</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>233</v>
+        <v>82</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>82</v>
@@ -6226,10 +6228,10 @@
         <v>191</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6304,7 +6306,7 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6347,7 +6349,7 @@
         <v>140</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>142</v>
@@ -6391,7 +6393,7 @@
         <v>198</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
@@ -6424,7 +6426,7 @@
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6584,10 +6586,10 @@
         <v>191</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6662,7 +6664,7 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6747,7 +6749,7 @@
         <v>198</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>82</v>
@@ -6940,10 +6942,10 @@
         <v>191</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7018,7 +7020,7 @@
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -7103,7 +7105,7 @@
         <v>198</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>82</v>
@@ -7532,10 +7534,10 @@
         <v>191</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7610,7 +7612,7 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7695,7 +7697,7 @@
         <v>198</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>82</v>
@@ -8124,10 +8126,10 @@
         <v>191</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8202,7 +8204,7 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8287,7 +8289,7 @@
         <v>198</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>82</v>
@@ -8956,10 +8958,10 @@
         <v>191</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -9034,7 +9036,7 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -9119,7 +9121,7 @@
         <v>198</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>82</v>
@@ -9312,10 +9314,10 @@
         <v>191</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9390,7 +9392,7 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9475,7 +9477,7 @@
         <v>198</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>82</v>
@@ -9904,10 +9906,10 @@
         <v>191</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9982,7 +9984,7 @@
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -10067,7 +10069,7 @@
         <v>198</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>82</v>
@@ -10498,10 +10500,10 @@
         <v>191</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10576,7 +10578,7 @@
         <v>82</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10661,7 +10663,7 @@
         <v>198</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>82</v>
@@ -11330,10 +11332,10 @@
         <v>191</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11408,7 +11410,7 @@
         <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11493,7 +11495,7 @@
         <v>198</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>82</v>
@@ -11686,10 +11688,10 @@
         <v>191</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11764,7 +11766,7 @@
         <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11849,7 +11851,7 @@
         <v>198</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>82</v>
@@ -12278,10 +12280,10 @@
         <v>191</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12356,7 +12358,7 @@
         <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12441,7 +12443,7 @@
         <v>198</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>82</v>
@@ -12752,10 +12754,10 @@
         <v>191</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12830,7 +12832,7 @@
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12873,7 +12875,7 @@
         <v>140</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>142</v>
@@ -12917,7 +12919,7 @@
         <v>198</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>82</v>
@@ -12950,7 +12952,7 @@
         <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12987,19 +12989,19 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13112,10 +13114,10 @@
         <v>191</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13190,7 +13192,7 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13233,7 +13235,7 @@
         <v>140</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>142</v>
@@ -13277,7 +13279,7 @@
         <v>198</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>82</v>
@@ -13310,7 +13312,7 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -14196,10 +14198,10 @@
         <v>191</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14274,7 +14276,7 @@
         <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14359,7 +14361,7 @@
         <v>198</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>82</v>
@@ -16480,10 +16482,10 @@
         <v>191</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16558,7 +16560,7 @@
         <v>82</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>82</v>
@@ -16601,7 +16603,7 @@
         <v>140</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>142</v>
@@ -16678,7 +16680,7 @@
         <v>82</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>82</v>
@@ -17918,10 +17920,10 @@
         <v>191</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17996,7 +17998,7 @@
         <v>82</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>82</v>
@@ -18039,7 +18041,7 @@
         <v>140</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N130" t="s" s="2">
         <v>142</v>
@@ -18116,7 +18118,7 @@
         <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>82</v>
@@ -19012,10 +19014,10 @@
         <v>191</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19090,7 +19092,7 @@
         <v>82</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>82</v>
@@ -19368,10 +19370,10 @@
         <v>95</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -19446,7 +19448,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -19531,7 +19533,7 @@
         <v>198</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>82</v>
@@ -20698,10 +20700,10 @@
         <v>191</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -20776,7 +20778,7 @@
         <v>82</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>82</v>
@@ -20819,7 +20821,7 @@
         <v>140</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N153" t="s" s="2">
         <v>142</v>
@@ -20896,7 +20898,7 @@
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>82</v>

--- a/resolveIssues/ig/StructureDefinition-fr-observation-survey-document.xlsx
+++ b/resolveIssues/ig/StructureDefinition-fr-observation-survey-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T08:54:45+00:00</t>
+    <t>2026-06-04T14:47:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
